--- a/working-example/DGF-V1.xlsx
+++ b/working-example/DGF-V1.xlsx
@@ -12,51 +12,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
-  <si>
-    <t xml:space="preserve">vname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vlabel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vdesc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vname_alias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vscope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vloc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duplicates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dd_f_level</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="240">
+  <si>
+    <t xml:space="preserve">var_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dd_vname_alias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dd_vlabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dd_vdesc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dd_f_levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_subtype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_data_import_rule</t>
   </si>
   <si>
     <t xml:space="preserve">raw_first5</t>
   </si>
   <si>
-    <t xml:space="preserve">raw_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vconvert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vtype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vtype_class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vlength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vformat</t>
+    <t xml:space="preserve">raw_duplicated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_subtype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable_data_import_rule</t>
   </si>
   <si>
     <t xml:space="preserve">rg_properties</t>
@@ -71,19 +92,31 @@
     <t xml:space="preserve">rg_graphics</t>
   </si>
   <si>
-    <t xml:space="preserve">rg_hash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dgf_standardize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dgf_validate</t>
+    <t xml:space="preserve">rg_max_chr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">validate_rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">validate_format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prov_start_hash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prov_current_hash</t>
   </si>
   <si>
     <t xml:space="preserve">F9_00_ORG_NAME_L1</t>
   </si>
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
   </si>
   <si>
     <t xml:space="preserve">INTERNATIONAL UNI... ;; 
@@ -91,9 +124,6 @@
 MORRIS COUNTY FAR... ;; 
 NATIONAL ASSOCIAT... ;; 
 AMERICAN MEAD MAK...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">character</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -645,14 +675,17 @@
     <t xml:space="preserve">EIN</t>
   </si>
   <si>
+    <t xml:space="preserve">numeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">number</t>
+  </si>
+  <si>
     <t xml:space="preserve">113161527 ;; 
 540354670 ;; 
 751627109 ;; 
 61636713 ;; 
 542015951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numeric</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -827,6 +860,9 @@
   </si>
   <si>
     <t xml:space="preserve">factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">categorical</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -1565,7 +1601,7 @@
 Y</t>
   </si>
   <si>
-    <t xml:space="preserve">logical</t>
+    <t xml:space="preserve">boolean</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -3357,65 +3393,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI Black"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI Black"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Lucida Console"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF404040"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44546A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF833C0C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF2EC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3430,41 +3422,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3754,1933 +3713,2665 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="20.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="20.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="20.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="20.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="20.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="20.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="20.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="20.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="20.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="20.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="20.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="20.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="20.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="20.71" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" t="s">
+        <v>57</v>
+      </c>
+      <c r="X5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5" t="n">
         <v>22</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="10" t="b">
+      <c r="AB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="8" t="n">
+      <c r="O6" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" t="s">
+        <v>32</v>
+      </c>
+      <c r="W6" t="s">
+        <v>66</v>
+      </c>
+      <c r="X6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W7" t="s">
+        <v>76</v>
+      </c>
+      <c r="X7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P9" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9" t="s">
+        <v>32</v>
+      </c>
+      <c r="W9" t="s">
+        <v>91</v>
+      </c>
+      <c r="X9" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
         <v>97</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>23</v>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W10" t="s">
+        <v>99</v>
+      </c>
+      <c r="X10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="10" t="b">
+    <row r="11">
+      <c r="A11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>105</v>
+      </c>
+      <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="n">
+      <c r="O11" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="8" t="s">
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U11" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11" t="s">
+        <v>106</v>
+      </c>
+      <c r="X11" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>23</v>
+      <c r="H12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" t="s">
+        <v>113</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" t="s">
+        <v>32</v>
+      </c>
+      <c r="V12" t="s">
+        <v>32</v>
+      </c>
+      <c r="W12" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="10" t="b">
+    <row r="13">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" t="s">
+        <v>121</v>
+      </c>
+      <c r="N13" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>23</v>
+      <c r="O13" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" t="s">
+        <v>32</v>
+      </c>
+      <c r="U13" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13" t="s">
+        <v>32</v>
+      </c>
+      <c r="W13" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="10" t="b">
+    <row r="14">
+      <c r="A14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" t="s">
+        <v>129</v>
+      </c>
+      <c r="N14" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>23</v>
+      <c r="O14" t="s">
+        <v>74</v>
+      </c>
+      <c r="P14" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" t="s">
+        <v>32</v>
+      </c>
+      <c r="T14" t="s">
+        <v>32</v>
+      </c>
+      <c r="U14" t="s">
+        <v>32</v>
+      </c>
+      <c r="V14" t="s">
+        <v>32</v>
+      </c>
+      <c r="W14" t="s">
+        <v>130</v>
+      </c>
+      <c r="X14" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="10" t="b">
+    <row r="15">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" t="s">
+        <v>137</v>
+      </c>
+      <c r="N15" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>23</v>
+      <c r="O15" t="s">
+        <v>74</v>
+      </c>
+      <c r="P15" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" t="s">
+        <v>32</v>
+      </c>
+      <c r="W15" t="s">
+        <v>139</v>
+      </c>
+      <c r="X15" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="10" t="b">
+    <row r="16">
+      <c r="A16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" t="s">
+        <v>146</v>
+      </c>
+      <c r="N16" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="O16" t="s">
+        <v>74</v>
+      </c>
+      <c r="P16" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
+      </c>
+      <c r="U16" t="s">
+        <v>32</v>
+      </c>
+      <c r="V16" t="s">
+        <v>32</v>
+      </c>
+      <c r="W16" t="s">
+        <v>147</v>
+      </c>
+      <c r="X16" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" t="s">
+        <v>153</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
         <v>63</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="P17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
+      </c>
+      <c r="U17" t="s">
+        <v>32</v>
+      </c>
+      <c r="V17" t="s">
+        <v>32</v>
+      </c>
+      <c r="W17" t="s">
+        <v>154</v>
+      </c>
+      <c r="X17" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>160</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>63</v>
+      </c>
+      <c r="P18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18" t="s">
+        <v>161</v>
+      </c>
+      <c r="X18" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" t="s">
+        <v>168</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
+      </c>
+      <c r="U19" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" t="s">
+        <v>32</v>
+      </c>
+      <c r="W19" t="s">
+        <v>169</v>
+      </c>
+      <c r="X19" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" t="s">
+        <v>176</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" t="s">
+        <v>32</v>
+      </c>
+      <c r="W20" t="s">
+        <v>177</v>
+      </c>
+      <c r="X20" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" t="s">
+        <v>184</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
+      </c>
+      <c r="U21" t="s">
+        <v>32</v>
+      </c>
+      <c r="V21" t="s">
+        <v>32</v>
+      </c>
+      <c r="W21" t="s">
+        <v>185</v>
+      </c>
+      <c r="X21" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" t="s">
+        <v>192</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" t="s">
+        <v>193</v>
+      </c>
+      <c r="X22" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="8" t="s">
+      <c r="AB22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
         <v>64</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>23</v>
+      <c r="H23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" t="s">
+        <v>199</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>63</v>
+      </c>
+      <c r="P23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" t="s">
+        <v>32</v>
+      </c>
+      <c r="W23" t="s">
+        <v>200</v>
+      </c>
+      <c r="X23" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="10" t="b">
+    <row r="24">
+      <c r="A24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" t="s">
+        <v>206</v>
+      </c>
+      <c r="N24" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>23</v>
+      <c r="O24" t="s">
+        <v>63</v>
+      </c>
+      <c r="P24" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" t="s">
+        <v>32</v>
+      </c>
+      <c r="V24" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" t="s">
+        <v>207</v>
+      </c>
+      <c r="X24" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="10" t="b">
+    <row r="25">
+      <c r="A25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" t="s">
+        <v>213</v>
+      </c>
+      <c r="N25" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="10" t="s">
+      <c r="O25" t="s">
         <v>63</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="P25" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" t="s">
+        <v>32</v>
+      </c>
+      <c r="U25" t="s">
+        <v>32</v>
+      </c>
+      <c r="V25" t="s">
+        <v>32</v>
+      </c>
+      <c r="W25" t="s">
+        <v>214</v>
+      </c>
+      <c r="X25" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" t="s">
         <v>63</v>
       </c>
-      <c r="N9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="R9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V9" s="7" t="s">
-        <v>23</v>
+      <c r="G26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" t="s">
+        <v>220</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>63</v>
+      </c>
+      <c r="P26" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" t="s">
+        <v>32</v>
+      </c>
+      <c r="T26" t="s">
+        <v>32</v>
+      </c>
+      <c r="U26" t="s">
+        <v>32</v>
+      </c>
+      <c r="V26" t="s">
+        <v>32</v>
+      </c>
+      <c r="W26" t="s">
+        <v>221</v>
+      </c>
+      <c r="X26" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>225</v>
       </c>
     </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="10" t="b">
+    <row r="27">
+      <c r="A27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>226</v>
+      </c>
+      <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" t="s">
+        <v>227</v>
+      </c>
+      <c r="N27" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="O27" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="P27" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" t="s">
+        <v>32</v>
+      </c>
+      <c r="U27" t="s">
+        <v>32</v>
+      </c>
+      <c r="V27" t="s">
+        <v>32</v>
+      </c>
+      <c r="W27" t="s">
+        <v>228</v>
+      </c>
+      <c r="X27" t="s">
+        <v>229</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
         <v>63</v>
       </c>
-      <c r="N10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="10" t="b">
+      <c r="G28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" t="s">
+        <v>234</v>
+      </c>
+      <c r="N28" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V11" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="O28" t="s">
         <v>63</v>
       </c>
-      <c r="M12" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="T12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="U12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V12" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q13" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="S14" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="U14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q15" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="N16" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="U16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V16" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="S17" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V17" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="T18" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="U18" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V18" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q19" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="S19" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V19" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="R20" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="S20" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V20" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="R21" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V21" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="S22" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V22" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N23" s="8" t="n">
+      <c r="P28" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" t="s">
+        <v>32</v>
+      </c>
+      <c r="T28" t="s">
+        <v>32</v>
+      </c>
+      <c r="U28" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" t="s">
+        <v>32</v>
+      </c>
+      <c r="W28" t="s">
+        <v>235</v>
+      </c>
+      <c r="X28" t="s">
+        <v>236</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA28" t="n">
         <v>10</v>
       </c>
-      <c r="O23" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="R23" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="S23" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="T23" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="U23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V24" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P25" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="S25" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="U25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V25" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="T26" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="U26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V26" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P27" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="R27" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="S27" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="T27" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V27" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="R28" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="S28" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="T28" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="U28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="V28" s="7" t="s">
-        <v>23</v>
+      <c r="AB28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
